--- a/02_Zero_Shot/outputs/NLI/BART-large-MNLI/RESULT_f-droid_bart-large-mnli_zeroshot.xlsx
+++ b/02_Zero_Shot/outputs/NLI/BART-large-MNLI/RESULT_f-droid_bart-large-mnli_zeroshot.xlsx
@@ -48836,7 +48836,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>73.15933461900022</v>
+        <v>97.45559406300163</v>
       </c>
     </row>
     <row r="8">
@@ -48846,7 +48846,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02575126174551222</v>
+        <v>0.03430327140549159</v>
       </c>
     </row>
   </sheetData>
